--- a/processo_2/synthetic_proposals/PROPOSTA_024/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_024/ficha_pontuacao.xlsx
@@ -523,13 +523,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>8.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>5.5</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7912-9855</t>
+          <t>3177-8018</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -816,8 +816,16 @@
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Revista Científica Avançada 2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1003-9616</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -958,7 +966,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -981,7 +989,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1050,17 +1058,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr"/>
     </row>
@@ -1075,7 +1083,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>6.5</v>
+        <v>19</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1118,7 +1126,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1141,7 +1149,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1187,7 +1195,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1210,7 +1218,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1233,17 +1241,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr"/>
     </row>
@@ -1256,17 +1264,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1279,7 +1287,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1302,17 +1310,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>1.5</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1325,17 +1333,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>1.5</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
@@ -1543,17 +1551,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
@@ -1566,7 +1574,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1612,17 +1620,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1635,7 +1643,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1660,7 +1668,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1858,7 +1866,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>24.5</v>
+        <v>30</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
